--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -1411,7 +1411,7 @@
     <t>ServiceRequest.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1918" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="484">
   <si>
     <t>Property</t>
   </si>
@@ -872,6 +872,9 @@
     <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
+    <t>要求されたサービスの分類。 (Yōkyū sa reta sābisu no bunrui.)</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
   </si>
   <si>
@@ -955,6 +958,9 @@
     <t>多くの検査・放射線処置コードは、血清または血漿グルコース、胸部 X 線など、検体・器官系が検査オーダー名に埋め込まれている。検体は、検査コードとは別に記録されないかもしれない。</t>
   </si>
   <si>
+    <t>指定された個人、組織、または医療サービスによって実施できるテストやサービスのコード。ラボの場合、LOINCが（preferred）[http://build.fhir.org/terminologies.html#preferred]であり、LOINCオーダーコードを使用した値セットが[こちら]（valueset-diagnostic-requests.html）で利用可能です。</t>
+  </si>
+  <si>
     <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
   </si>
   <si>
@@ -987,6 +993,9 @@
   </si>
   <si>
     <t>リクエストされたサービス提供の指示についての医療記録からの情報については、supportingInformation要素を使用。</t>
+  </si>
+  <si>
+    <t>「注文コンテキストに基づくコード化された注文詳細。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
@@ -1860,7 +1869,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="65.953125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="194.140625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -4989,9 +4998,11 @@
       <c r="X27" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y27" s="2"/>
+      <c r="Y27" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
@@ -5027,10 +5038,10 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>268</v>
@@ -5041,10 +5052,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5070,10 +5081,10 @@
         <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5081,7 +5092,7 @@
         <v>82</v>
       </c>
       <c r="Q28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="R28" t="s" s="2">
         <v>82</v>
@@ -5105,10 +5116,10 @@
         <v>252</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5126,7 +5137,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5141,16 +5152,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5158,10 +5169,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5184,70 +5195,70 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="P29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="R29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="L29" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="M29" t="s" s="2">
-        <v>291</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="P29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="R29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5262,13 +5273,13 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
@@ -5279,14 +5290,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5308,13 +5319,13 @@
         <v>270</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5342,9 +5353,11 @@
       <c r="X30" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y30" s="2"/>
+      <c r="Y30" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="Z30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
@@ -5362,7 +5375,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5377,31 +5390,31 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5423,13 +5436,13 @@
         <v>270</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5457,9 +5470,11 @@
       <c r="X31" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y31" s="2"/>
+      <c r="Y31" t="s" s="2">
+        <v>315</v>
+      </c>
       <c r="Z31" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
@@ -5477,7 +5492,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5486,7 +5501,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
@@ -5495,24 +5510,24 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5535,19 +5550,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5596,7 +5611,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5614,10 +5629,10 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -5628,10 +5643,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5654,13 +5669,13 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5711,7 +5726,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>91</v>
@@ -5726,31 +5741,31 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5769,13 +5784,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5826,7 +5841,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5841,31 +5856,31 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5884,13 +5899,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5941,7 +5956,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5956,27 +5971,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5999,13 +6014,13 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6035,10 +6050,10 @@
         <v>157</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6056,7 +6071,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6077,25 +6092,25 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6114,13 +6129,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6171,7 +6186,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6186,31 +6201,31 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6229,16 +6244,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6288,7 +6303,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6303,31 +6318,31 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6349,13 +6364,13 @@
         <v>270</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6384,10 +6399,10 @@
         <v>157</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -6405,7 +6420,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6420,16 +6435,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6437,14 +6452,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6463,16 +6478,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6522,7 +6537,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6537,16 +6552,16 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6554,10 +6569,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6583,10 +6598,10 @@
         <v>270</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6616,28 +6631,28 @@
         <v>157</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6658,10 +6673,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6669,10 +6684,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6695,13 +6710,13 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6752,7 +6767,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6773,10 +6788,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6784,10 +6799,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6813,13 +6828,13 @@
         <v>270</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6848,10 +6863,10 @@
         <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -6869,7 +6884,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6884,16 +6899,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6901,10 +6916,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6927,16 +6942,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6986,7 +7001,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7001,16 +7016,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7018,10 +7033,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7044,13 +7059,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7101,7 +7116,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7116,13 +7131,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7133,14 +7148,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7159,16 +7174,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7218,7 +7233,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7233,13 +7248,13 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7250,10 +7265,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7276,16 +7291,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7335,7 +7350,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7353,10 +7368,10 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -7367,14 +7382,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7396,16 +7411,16 @@
         <v>270</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7433,10 +7448,10 @@
         <v>157</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7454,7 +7469,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7472,24 +7487,24 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7512,13 +7527,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7569,7 +7584,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7584,27 +7599,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7630,10 +7645,10 @@
         <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7684,7 +7699,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7702,10 +7717,10 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -7716,10 +7731,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7742,16 +7757,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7801,7 +7816,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7816,13 +7831,13 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>190</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -4247,7 +4247,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-18</t>
+    <t>2024-11-18</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="483">
   <si>
     <t>Property</t>
   </si>
@@ -699,9 +699,6 @@
   </si>
   <si>
     <t>このサービスリクエストに部分的、または完全に関わる、外部の管理されたプロトコール、ガイドライン、オーダセットや他の定義へのURL参照</t>
-  </si>
-  <si>
-    <t>これはHTMLページ、PDFなどであるか、解決不能なURI識別子である可能性があります。</t>
   </si>
   <si>
     <t>HTMLページ、PDFなど、名前で解決できないURI識別子</t>
@@ -4247,7 +4244,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4279,7 +4276,7 @@
         <v>82</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>82</v>
@@ -4333,7 +4330,7 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>215</v>
@@ -4350,14 +4347,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4376,13 +4373,13 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4433,7 +4430,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4448,13 +4445,13 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -4465,14 +4462,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4491,13 +4488,13 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4548,7 +4545,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4563,13 +4560,13 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>238</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -4580,14 +4577,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4609,16 +4606,16 @@
         <v>200</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4667,7 +4664,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4682,13 +4679,13 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -4699,10 +4696,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4728,13 +4725,13 @@
         <v>167</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4760,14 +4757,14 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>254</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4784,7 +4781,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -4799,27 +4796,27 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>256</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>257</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>259</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4845,13 +4842,13 @@
         <v>167</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4877,14 +4874,14 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
@@ -4901,7 +4898,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -4916,16 +4913,16 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>190</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4933,10 +4930,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4959,19 +4956,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>271</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4999,11 +4996,11 @@
         <v>157</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5020,7 +5017,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5038,13 +5035,13 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>278</v>
-      </c>
       <c r="AN27" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5052,10 +5049,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5081,10 +5078,10 @@
         <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5092,35 +5089,35 @@
         <v>82</v>
       </c>
       <c r="Q28" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="R28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="Y28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="R28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>284</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5137,7 +5134,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5152,16 +5149,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5169,10 +5166,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5195,26 +5192,26 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="O29" t="s" s="2">
+      <c r="P29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="P29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>295</v>
-      </c>
       <c r="R29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5258,7 +5255,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5273,13 +5270,13 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
@@ -5290,14 +5287,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5316,16 +5313,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5354,11 +5351,11 @@
         <v>157</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5375,7 +5372,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5390,31 +5387,31 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>309</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5433,16 +5430,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5471,11 +5468,11 @@
         <v>157</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>316</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5492,7 +5489,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5501,7 +5498,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
@@ -5510,24 +5507,24 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5550,19 +5547,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5611,7 +5608,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5629,10 +5626,10 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -5643,10 +5640,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5669,13 +5666,13 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5726,7 +5723,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>91</v>
@@ -5741,31 +5738,31 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>334</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5784,13 +5781,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>338</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>339</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5841,7 +5838,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5856,31 +5853,31 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5899,13 +5896,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5956,7 +5953,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5971,27 +5968,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>354</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6014,13 +6011,13 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6050,11 +6047,11 @@
         <v>157</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>360</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6071,7 +6068,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6092,25 +6089,25 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>362</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6129,13 +6126,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6186,7 +6183,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6201,31 +6198,31 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>372</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6244,16 +6241,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6303,7 +6300,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6318,31 +6315,31 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>383</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6361,16 +6358,16 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6399,11 +6396,11 @@
         <v>157</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>390</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6420,7 +6417,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6435,16 +6432,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6452,14 +6449,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6478,16 +6475,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>399</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>400</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6537,7 +6534,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6552,16 +6549,16 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>403</v>
-      </c>
       <c r="AN40" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6569,10 +6566,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6595,13 +6592,13 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>406</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6631,11 +6628,11 @@
         <v>157</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>408</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6652,7 +6649,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6673,10 +6670,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6684,10 +6681,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6710,13 +6707,13 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6767,7 +6764,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6788,10 +6785,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6799,10 +6796,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6825,16 +6822,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6863,11 +6860,11 @@
         <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>420</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6884,7 +6881,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6899,16 +6896,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>423</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6916,10 +6913,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6942,16 +6939,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7001,7 +6998,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7016,16 +7013,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>432</v>
-      </c>
       <c r="AN44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7033,10 +7030,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7059,13 +7056,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>435</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7116,7 +7113,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7131,13 +7128,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7148,14 +7145,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7174,16 +7171,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7233,7 +7230,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7248,13 +7245,13 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7265,10 +7262,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7291,16 +7288,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>451</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7350,7 +7347,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7368,10 +7365,10 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -7382,14 +7379,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7408,19 +7405,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>459</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7448,11 +7445,11 @@
         <v>157</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>463</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7469,7 +7466,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7487,24 +7484,24 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>465</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7527,13 +7524,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7584,7 +7581,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7599,27 +7596,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>472</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7645,10 +7642,10 @@
         <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7699,7 +7696,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7717,10 +7714,10 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -7731,10 +7728,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7757,16 +7754,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7816,7 +7813,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7831,13 +7828,13 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>190</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -279,7 +279,7 @@
   </si>
   <si>
     <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}prr-1:コードが存在する場合に限り、注文詳細は存在するものとします。 {orderDetail.empty() or code.exists()}</t>
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}prr-1:コードが存在する場合に限り、注文詳細は存在するものとします。 {orderDetail.empty() or code.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -307,10 +307,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -323,10 +323,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -369,7 +369,7 @@
     <t>実装によって定義される追加コンテンツ</t>
   </si>
   <si>
-    <t>「要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。」</t>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。</t>
   </si>
   <si>
     <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。</t>
@@ -389,16 +389,16 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ServiceRequest.meta.versionId</t>
   </si>
   <si>
-    <t>バージョン固有の識別子</t>
-  </si>
-  <si>
-    <t>URLのバージョン部分に表示されるバージョン固有の識別子。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi)</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。</t>
   </si>
   <si>
     <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。</t>
@@ -414,7 +414,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースのバージョンが最後に変更されたとき」</t>
+    <t>リソースのバージョンが最後に変更されたとき</t>
   </si>
   <si>
     <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。</t>
@@ -439,8 +439,8 @@
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
   </si>
   <si>
-    <t>「プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
-この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。」</t>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。</t>
   </si>
   <si>
     <t>Meta.source</t>
@@ -508,7 +508,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>「様々なタグを表すコードで、一般的にはワークフローに関連しています。</t>
+    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/common-tags</t>
@@ -523,7 +523,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -539,10 +539,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」(Risōsukontentsu no gengo)</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>「リソースコンテンツの言語」</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -551,7 +551,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」(Ningen no gengo.)</t>
+    <t>「人間の言語。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -571,10 +571,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -597,13 +597,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」(Fukuma rete iru, inrain no risōsu)</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>「含まれている、インラインのリソース」</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -615,7 +615,7 @@
     <t>ServiceRequest.extension</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります」</t>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
@@ -627,7 +627,7 @@
     <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -747,7 +747,7 @@
     <t>完了または終了したService Requestリソースの代替（への参照）</t>
   </si>
   <si>
-    <t>「そのリクエストは、参照された完了または終了したリクエストの代わりを占めます。」</t>
+    <t>そのリクエストは、参照された完了または終了したリクエストの代わりを占めます。</t>
   </si>
   <si>
     <t>Request.replaces</t>
@@ -835,7 +835,7 @@
     <t>この要素は、リソースが実際に適用されるタイミングや方法を意図的に変更するため、修飾子と表現される。</t>
   </si>
   <si>
-    <t>「サービスのリクエストの種類」</t>
+    <t>サービスのリクエストの種類</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
@@ -893,7 +893,7 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>「リクエストの対処に割り当てるべき重要度のレベルを特定する。」</t>
+    <t>リクエストの対処に割り当てるべき重要度のレベルを特定する。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
@@ -992,7 +992,7 @@
     <t>リクエストされたサービス提供の指示についての医療記録からの情報については、supportingInformation要素を使用。</t>
   </si>
   <si>
-    <t>「注文コンテキストに基づくコード化された注文詳細。」</t>
+    <t>注文コンテキストに基づくコード化された注文詳細。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
@@ -1227,7 +1227,7 @@
     <t>参加者の資格ではなく役割。タスクではなく、能力を記述。例えば、「調剤薬局」、「精神科医」、「院内紹介」など。</t>
   </si>
   <si>
-    <t>「初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。」</t>
+    <t>初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/participant-role</t>
@@ -1283,7 +1283,7 @@
     <t>実際に行為が行われるべき好ましい場所を、コード化またはフリーテキスト形式で記述。例：自宅や介護施設など。</t>
   </si>
   <si>
-    <t>「サービスが提供される場所タイプ。」</t>
+    <t>サービスが提供される場所タイプ。</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="482">
   <si>
     <t>Property</t>
   </si>
@@ -278,8 +278,8 @@
     <t>診断のための検査、治療、手術などのサービスリクエストの記録</t>
   </si>
   <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}prr-1:コードが存在する場合に限り、注文詳細は存在するものとします。 {orderDetail.empty() or code.exists()}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}prr-1:コードが存在する場合に限り、注文詳細は存在するものとします。 {orderDetail.empty() or code.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -307,10 +307,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
-  </si>
-  <si>
-    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
+    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
+  </si>
+  <si>
+    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -323,10 +323,10 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するMetadata</t>
-  </si>
-  <si>
-    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>「リソースに関するメタデータ」</t>
+  </si>
+  <si>
+    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -505,15 +505,6 @@
     <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。</t>
   </si>
   <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>様々なタグを表すコードで、一般的にはワークフローに関連しています。例：「ジョーンズ博士によるレビューが必要です」。</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
-  </si>
-  <si>
     <t>Meta.tag</t>
   </si>
   <si>
@@ -523,7 +514,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
+    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -542,7 +533,7 @@
     <t>「リソースコンテンツの言語」</t>
   </si>
   <si>
-    <t>リソースが書かれている基本言語。</t>
+    <t>「リソースが書かれている基本言語。」</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -571,10 +562,10 @@
 </t>
   </si>
   <si>
-    <t>人間の解釈のためのリソースのテキスト要約</t>
-  </si>
-  <si>
-    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
+    <t>「人間の解釈のためのリソースのテキスト要約」</t>
+  </si>
+  <si>
+    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -600,10 +591,10 @@
     <t>「含まれている、インラインのリソース」</t>
   </si>
   <si>
-    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
-  </si>
-  <si>
-    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
+    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
+  </si>
+  <si>
+    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -615,19 +606,23 @@
     <t>ServiceRequest.extension</t>
   </si>
   <si>
-    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります</t>
+    <t>「リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります」</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
+ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>ServiceRequest.modifierExtension</t>
   </si>
   <si>
-    <t>無視できない拡張機能 (Mushi dekinai kakuchou kinou)</t>
-  </si>
-  <si>
-    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
+    <t xml:space="preserve">無視できない拡張機能 </t>
+  </si>
+  <si>
+    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -747,7 +742,7 @@
     <t>完了または終了したService Requestリソースの代替（への参照）</t>
   </si>
   <si>
-    <t>そのリクエストは、参照された完了または終了したリクエストの代わりを占めます。</t>
+    <t>「そのリクエストは、参照された完了または終了したリクエストの代わりを占めます。」</t>
   </si>
   <si>
     <t>Request.replaces</t>
@@ -835,7 +830,7 @@
     <t>この要素は、リソースが実際に適用されるタイミングや方法を意図的に変更するため、修飾子と表現される。</t>
   </si>
   <si>
-    <t>サービスのリクエストの種類</t>
+    <t>「サービスのリクエストの種類」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
@@ -869,7 +864,10 @@
     <t>Used for filtering what service request are retrieved and displayed.</t>
   </si>
   <si>
-    <t>要求されたサービスの分類。 (Yōkyū sa reta sābisu no bunrui.)</t>
+    <t>example</t>
+  </si>
+  <si>
+    <t>要求されたサービスの分類。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
@@ -893,7 +891,7 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>リクエストの対処に割り当てるべき重要度のレベルを特定する。</t>
+    <t>「リクエストの対処に割り当てるべき重要度のレベルを特定する。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
@@ -992,7 +990,7 @@
     <t>リクエストされたサービス提供の指示についての医療記録からの情報については、supportingInformation要素を使用。</t>
   </si>
   <si>
-    <t>注文コンテキストに基づくコード化された注文詳細。</t>
+    <t>「注文コンテキストに基づくコード化された注文詳細。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
@@ -1227,7 +1225,7 @@
     <t>参加者の資格ではなく役割。タスクではなく、能力を記述。例えば、「調剤薬局」、「精神科医」、「院内紹介」など。</t>
   </si>
   <si>
-    <t>初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。</t>
+    <t>「初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。」</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/participant-role</t>
@@ -1283,7 +1281,7 @@
     <t>実際に行為が行われるべき好ましい場所を、コード化またはフリーテキスト形式で記述。例：自宅や介護施設など。</t>
   </si>
   <si>
-    <t>サービスが提供される場所タイプ。</t>
+    <t>「サービスが提供される場所タイプ。」</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
@@ -3236,31 +3234,31 @@
         <v>82</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="Y12" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="Z12" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3292,10 +3290,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3321,13 +3319,13 @@
         <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3377,7 +3375,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3409,10 +3407,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3435,16 +3433,16 @@
         <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3470,31 +3468,31 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -3526,14 +3524,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3552,16 +3550,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3611,7 +3609,7 @@
         <v>82</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -3632,7 +3630,7 @@
         <v>82</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>82</v>
@@ -3643,14 +3641,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3669,16 +3667,16 @@
         <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="L16" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>185</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3728,7 +3726,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -3749,7 +3747,7 @@
         <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>82</v>
@@ -3760,10 +3758,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3792,7 +3790,7 @@
         <v>113</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>115</v>
@@ -3845,7 +3843,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3857,7 +3855,7 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -3866,7 +3864,7 @@
         <v>82</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>82</v>
@@ -3877,10 +3875,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3906,16 +3904,16 @@
         <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -3964,7 +3962,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3976,7 +3974,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -3985,7 +3983,7 @@
         <v>82</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>82</v>
@@ -3996,10 +3994,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4022,16 +4020,16 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4081,7 +4079,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4096,27 +4094,27 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>208</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4139,16 +4137,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4198,7 +4196,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4213,13 +4211,13 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>214</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
@@ -4230,10 +4228,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4259,13 +4257,13 @@
         <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>218</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4315,7 +4313,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4330,13 +4328,13 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>82</v>
@@ -4347,14 +4345,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4373,13 +4371,13 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4430,7 +4428,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4445,13 +4443,13 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -4462,14 +4460,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4488,13 +4486,13 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>232</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>234</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4545,7 +4543,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4560,13 +4558,13 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>237</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -4577,14 +4575,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4603,19 +4601,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4664,7 +4662,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4679,13 +4677,13 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>246</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -4696,10 +4694,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4722,16 +4720,16 @@
         <v>92</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>248</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4757,14 +4755,14 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="Z25" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>253</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4781,7 +4779,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -4796,27 +4794,27 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL25" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AM25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>258</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4839,16 +4837,16 @@
         <v>92</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4874,13 +4872,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -4898,7 +4896,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -4913,16 +4911,16 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4930,10 +4928,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4956,19 +4954,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>270</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4993,14 +4991,14 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>274</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>275</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5017,7 +5015,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5035,13 +5033,13 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>276</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>277</v>
-      </c>
       <c r="AN27" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5049,10 +5047,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5075,13 +5073,13 @@
         <v>92</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5089,35 +5087,35 @@
         <v>82</v>
       </c>
       <c r="Q28" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="R28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="Y28" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="R28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>282</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>283</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5134,7 +5132,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5149,16 +5147,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5166,10 +5164,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5192,26 +5190,26 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="O29" t="s" s="2">
+      <c r="P29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s" s="2">
         <v>293</v>
       </c>
-      <c r="P29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>294</v>
-      </c>
       <c r="R29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5255,7 +5253,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5270,13 +5268,13 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>295</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
@@ -5287,14 +5285,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5313,16 +5311,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5348,14 +5346,14 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>303</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5372,7 +5370,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5387,31 +5385,31 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>308</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5430,16 +5428,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5465,14 +5463,14 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>315</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5489,7 +5487,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5498,7 +5496,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
@@ -5507,24 +5505,24 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5547,19 +5545,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>323</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5608,7 +5606,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5626,10 +5624,10 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -5640,10 +5638,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5666,13 +5664,13 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5723,7 +5721,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>91</v>
@@ -5738,31 +5736,31 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5781,13 +5779,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5838,7 +5836,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5853,31 +5851,31 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>343</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5896,13 +5894,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5953,7 +5951,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5968,27 +5966,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>353</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6011,13 +6009,13 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6044,14 +6042,14 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>359</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6068,7 +6066,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6089,25 +6087,25 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>361</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6126,13 +6124,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6183,7 +6181,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6198,31 +6196,31 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>370</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>371</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6241,16 +6239,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6300,7 +6298,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6315,31 +6313,31 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>382</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6358,16 +6356,16 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>387</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6393,14 +6391,14 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>389</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6417,7 +6415,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6432,16 +6430,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6449,14 +6447,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6475,16 +6473,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6534,7 +6532,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6549,16 +6547,16 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>402</v>
-      </c>
       <c r="AN40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6566,10 +6564,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6592,13 +6590,13 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6625,14 +6623,14 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6649,7 +6647,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6670,10 +6668,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6681,10 +6679,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6707,13 +6705,13 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6764,7 +6762,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6785,10 +6783,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6796,10 +6794,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6822,16 +6820,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6857,14 +6855,14 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6881,7 +6879,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6896,16 +6894,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6913,10 +6911,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6939,16 +6937,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6998,7 +6996,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7013,16 +7011,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AN44" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7030,10 +7028,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7056,13 +7054,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>435</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7113,7 +7111,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7128,13 +7126,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>437</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>438</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7145,14 +7143,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7171,16 +7169,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>442</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>443</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7230,7 +7228,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7245,13 +7243,13 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7262,10 +7260,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7288,16 +7286,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>450</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7347,7 +7345,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7365,10 +7363,10 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -7379,14 +7377,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7405,19 +7403,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7442,14 +7440,14 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>462</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7466,7 +7464,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7484,24 +7482,24 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>464</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7524,13 +7522,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>466</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>467</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>468</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7581,7 +7579,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7596,27 +7594,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>471</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7642,10 +7640,10 @@
         <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7696,7 +7694,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7714,10 +7712,10 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -7728,10 +7726,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7754,16 +7752,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7813,7 +7811,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7828,13 +7826,13 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>481</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>482</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="481">
   <si>
     <t>Property</t>
   </si>
@@ -278,8 +278,8 @@
     <t>診断のための検査、治療、手術などのサービスリクエストの記録</t>
   </si>
   <si>
-    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません . {contained.contained.empty()}
-dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:「もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。」 {contained.meta.security.empty()}dom-6:「資源は堅牢な管理のために物語を持つべきである。」 {text.`div`.exists()}prr-1:コードが存在する場合に限り、注文詳細は存在するものとします。 {orderDetail.empty() or code.exists()}</t>
+    <t>dom-2:もしリソースが他のリソースに含まれている場合、そのリソースにはネストされたリソースを含めてはなりません (moshi risōsu ga hoka no risōsu ni fukumarete iru baai, sono risōsu ni wa nesuto sareta risōsu o fukumete wa narimasen). {contained.contained.empty()}
+dom-3:もしリソースが他のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含まれるリソースに参照されるべきです。 {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:もしリソースが別のリソースの中に含まれる場合、meta.versionIdまたはmeta.lastUpdatedを持つべきではありません。 {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:もしリソースが他のリソースに含まれている場合、セキュリティラベルを持つべきではありません。 {contained.meta.security.empty()}dom-6:資源は堅牢な管理のために物語を持つべきである。 {text.`div`.exists()}prr-1:コードが存在する場合に限り、注文詳細は存在するものとします。 {orderDetail.empty() or code.exists()}</t>
   </si>
   <si>
     <t>Request</t>
@@ -307,10 +307,10 @@
     <t>このアーティファクトの論理ID</t>
   </si>
   <si>
-    <t>「リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。」</t>
-  </si>
-  <si>
-    <t>「リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。」</t>
+    <t>リソースのURLで使用される論理ID。一度割り当てられたら、この値は変更されません。</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、作成操作を使用してサーバーに送信されているときだけです。</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -323,10 +323,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースに関するメタデータ」</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
+    <t>リソースに関するMetadata</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これはインフラストラクチャによって維持されるコンテンツです。 コンテンツの変更は、リソースのバージョン変更と常に関連しているわけではありません。</t>
   </si>
   <si>
     <t>Resource.meta</t>
@@ -433,7 +433,7 @@
 </t>
   </si>
   <si>
-    <t>「リソースがどこから来たかを特定する」</t>
+    <t>リソースがどこから来たかを特定する</t>
   </si>
   <si>
     <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。</t>
@@ -514,7 +514,7 @@
     <t>このコンテンツが作成されたルールセット</t>
   </si>
   <si>
-    <t>「リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。」</t>
+    <t>リソース構築時に遵守された一連のルールを指すものであり、コンテンツを処理する際に理解する必要があります。しばしば、特別なルールを定義する実装ガイドとその他のプロファイルなどを含むものです。</t>
   </si>
   <si>
     <t>このルールセットを主張することで、取引先の限られた集団にしか内容を理解させることができず、長期的にはデータの有用性が制限されます。しかしながら、現存するヘルスエコシステムは高度に分断化しており、一般的に計算可能な形式でデータを定義、収集、交換する準備が整っていません。できる限り、実装者および/または仕様ライターはこの要素の使用を避けるべきです。使用する場合、URLは、そのナラティブとともに他のプロファイル、値セットなどを含む実装ガイドを定義する参照となります。</t>
@@ -530,10 +530,10 @@
 </t>
   </si>
   <si>
-    <t>「リソースコンテンツの言語」</t>
-  </si>
-  <si>
-    <t>「リソースが書かれている基本言語。」</t>
+    <t>リソースコンテンツの言語</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。</t>
   </si>
   <si>
     <t>言語はインデックスとアクセシビリティをサポートするために提供されます（通常、テキスト読み上げなどのサービスは言語タグを使用します）。物語のHTML言語タグは、物語に適用されます。リソース上の言語タグは、リソース内のデータから生成される他のプレゼンテーションの言語を指定するために使用できます。すべてのコンテンツが基本言語である必要はありません。Resource.languageは自動的に物語に適用されたと想定してはいけません。言語が指定されている場合、HTMLのdiv要素にも指定する必要があります（xml：langとhtml lang属性の関係に関する情報はHTML5の規則を参照）。</t>
@@ -542,7 +542,7 @@
     <t>preferred</t>
   </si>
   <si>
-    <t>「人間の言語。」</t>
+    <t>人間の言語。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages</t>
@@ -562,10 +562,10 @@
 </t>
   </si>
   <si>
-    <t>「人間の解釈のためのリソースのテキスト要約」</t>
-  </si>
-  <si>
-    <t>「リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。」</t>
+    <t>人間の解釈のためのリソースのテキスト要約</t>
+  </si>
+  <si>
+    <t>リソースの要約を含む人が読めるナビゲーションであり、リソースの内容を人に表現するために使用できます。ナビゲーションはすべての構造化されたデータをエンコードする必要はありませんが、人間がナビゲーションを読むだけで「臨床的に安全」であるために十分な詳細を含む必要があります。リソース定義には、臨床的な安全性を確保するためにナビゲーションで表現する必要があるコンテンツが定義される場合があります。</t>
   </si>
   <si>
     <t>含まれるリソースには説明がありません。含まれないリソースには説明が必要です。場合によっては、リソースが少量のデータしか含まず、テキストだけで表現されることがあります（minOccurs = 1要素がすべて満たされている限り）。これは、情報が「テキストの塊」としてキャプチャされるレガシーシステムからのデータや、テキストが生またはナレーションされて符号化された情報が後で追加される場合に必要な場合があります。</t>
@@ -588,13 +588,13 @@
 </t>
   </si>
   <si>
-    <t>「含まれている、インラインのリソース」</t>
-  </si>
-  <si>
-    <t>「これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。」</t>
-  </si>
-  <si>
-    <t>「コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。」</t>
+    <t>含まれている、インラインのリソース</t>
+  </si>
+  <si>
+    <t>これらのリソースは、それらを含むリソースから独立した存在を持ちません。それらは独立して識別することはできず、独自の独立したトランザクション範囲を持つこともできません。</t>
+  </si>
+  <si>
+    <t>コンテンツが適切に識別できる場合には、これを行うべきではありません。識別が失われると、再び復元することは非常に困難であり（文脈に依存します）、メタ要素にプロファイルとタグを持つことができますが、セキュリティのラベルを持っていてはいけません。</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
@@ -606,23 +606,19 @@
     <t>ServiceRequest.extension</t>
   </si>
   <si>
-    <t>「リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります」</t>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用することができます。拡張機能の使用を安全かつ管理可能にするために、定義と使用の一定のガバナンスが適用されます。実装者はどんな拡張機能でも定義できますが、拡張機能の定義の一部として満たす必要がある要件があります</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:「拡張機能または値[x]のいずれかが必要です。両方ではありません。」 {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
     <t>ServiceRequest.modifierExtension</t>
   </si>
   <si>
-    <t xml:space="preserve">無視できない拡張機能 </t>
-  </si>
-  <si>
-    <t>「リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。」</t>
+    <t>無視できない拡張機能</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義に含まれない、要素の理解や、それを含む要素の子孫の理解を修正する追加情報を表すためにも使用されることがあります。通常、修飾要素は否定や修飾を提供します。拡張機能の使用を安全で管理しやすくするために、拡張機能の定義と使用に対して厳格な統治が適用されます。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たす必要がある要件があります。リソースを処理するアプリケーションは、修飾子拡張をチェックする必要があります。修飾子拡張は、リソースまたはドメインリソースの任意の要素の意味を変更してはなりません（修飾子拡張自体の意味も変更できません）。</t>
   </si>
   <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
@@ -742,7 +738,7 @@
     <t>完了または終了したService Requestリソースの代替（への参照）</t>
   </si>
   <si>
-    <t>「そのリクエストは、参照された完了または終了したリクエストの代わりを占めます。」</t>
+    <t>そのリクエストは、参照された完了または終了したリクエストの代わりを占めます。</t>
   </si>
   <si>
     <t>Request.replaces</t>
@@ -797,7 +793,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>"サービスオーダーのステータス。"</t>
+    <t>サービスオーダーのステータス。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-status|4.0.1</t>
@@ -830,7 +826,7 @@
     <t>この要素は、リソースが実際に適用されるタイミングや方法を意図的に変更するため、修飾子と表現される。</t>
   </si>
   <si>
-    <t>「サービスのリクエストの種類」</t>
+    <t>サービスのリクエストの種類</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
@@ -891,7 +887,7 @@
     <t>If missing, this task should be performed with normal priority</t>
   </si>
   <si>
-    <t>「リクエストの対処に割り当てるべき重要度のレベルを特定する。」</t>
+    <t>リクエストの対処に割り当てるべき重要度のレベルを特定する。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
@@ -990,7 +986,7 @@
     <t>リクエストされたサービス提供の指示についての医療記録からの情報については、supportingInformation要素を使用。</t>
   </si>
   <si>
-    <t>「注文コンテキストに基づくコード化された注文詳細。」</t>
+    <t>注文コンテキストに基づくコード化された注文詳細。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
@@ -1225,7 +1221,7 @@
     <t>参加者の資格ではなく役割。タスクではなく、能力を記述。例えば、「調剤薬局」、「精神科医」、「院内紹介」など。</t>
   </si>
   <si>
-    <t>「初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。」</t>
+    <t>初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/participant-role</t>
@@ -1281,7 +1277,7 @@
     <t>実際に行為が行われるべき好ましい場所を、コード化またはフリーテキスト形式で記述。例：自宅や介護施設など。</t>
   </si>
   <si>
-    <t>「サービスが提供される場所タイプ。」</t>
+    <t>サービスが提供される場所タイプ。</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
@@ -3855,7 +3851,7 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>191</v>
+        <v>120</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -3875,10 +3871,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3904,16 +3900,16 @@
         <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>115</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -3962,7 +3958,7 @@
         <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3974,7 +3970,7 @@
         <v>82</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>191</v>
+        <v>120</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>82</v>
@@ -3994,10 +3990,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4020,16 +4016,16 @@
         <v>92</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4079,7 +4075,7 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4094,27 +4090,27 @@
         <v>103</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AM19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AN19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>206</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4137,16 +4133,16 @@
         <v>92</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>209</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>210</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>211</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4196,7 +4192,7 @@
         <v>82</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4211,13 +4207,13 @@
         <v>103</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AL20" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AM20" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>82</v>
@@ -4228,10 +4224,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4257,13 +4253,13 @@
         <v>133</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4313,7 +4309,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4328,13 +4324,13 @@
         <v>103</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AL21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>82</v>
@@ -4345,14 +4341,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4371,13 +4367,13 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4428,7 +4424,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4443,13 +4439,13 @@
         <v>103</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>82</v>
@@ -4460,14 +4456,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4486,13 +4482,13 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4543,7 +4539,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4558,13 +4554,13 @@
         <v>103</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>233</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>82</v>
@@ -4575,14 +4571,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4601,19 +4597,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M24" t="s" s="2">
         <v>238</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="N24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>240</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -4662,7 +4658,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4677,13 +4673,13 @@
         <v>103</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AM24" t="s" s="2">
         <v>243</v>
-      </c>
-      <c r="AM24" t="s" s="2">
-        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>82</v>
@@ -4694,10 +4690,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4723,13 +4719,13 @@
         <v>164</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4755,14 +4751,14 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y25" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="Y25" t="s" s="2">
+      <c r="Z25" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="Z25" t="s" s="2">
-        <v>251</v>
-      </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
       </c>
@@ -4779,7 +4775,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>91</v>
@@ -4794,27 +4790,27 @@
         <v>103</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>252</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>256</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4840,13 +4836,13 @@
         <v>164</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>258</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>260</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4872,14 +4868,14 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="Z26" t="s" s="2">
-        <v>262</v>
-      </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
@@ -4896,7 +4892,7 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>91</v>
@@ -4911,16 +4907,16 @@
         <v>103</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>187</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AN26" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -4928,10 +4924,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4954,19 +4950,19 @@
         <v>92</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>271</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -4991,14 +4987,14 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="Y27" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="Y27" t="s" s="2">
+      <c r="Z27" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>274</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5015,7 +5011,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5033,13 +5029,13 @@
         <v>82</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="AM27" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>276</v>
-      </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5047,10 +5043,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5076,10 +5072,10 @@
         <v>164</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5087,35 +5083,35 @@
         <v>82</v>
       </c>
       <c r="Q28" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="R28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="Y28" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="R28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X28" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="Y28" t="s" s="2">
+      <c r="Z28" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="Z28" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5132,7 +5128,7 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5147,16 +5143,16 @@
         <v>103</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="AL28" t="s" s="2">
+      <c r="AM28" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AM28" t="s" s="2">
+      <c r="AN28" t="s" s="2">
         <v>285</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>286</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>82</v>
@@ -5164,10 +5160,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5190,26 +5186,26 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="O29" t="s" s="2">
+      <c r="P29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q29" t="s" s="2">
         <v>292</v>
       </c>
-      <c r="P29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q29" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="R29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5253,7 +5249,7 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5268,13 +5264,13 @@
         <v>103</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>82</v>
@@ -5285,14 +5281,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5311,16 +5307,16 @@
         <v>92</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5346,14 +5342,14 @@
         <v>82</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Y30" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="Z30" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="Z30" t="s" s="2">
-        <v>302</v>
-      </c>
       <c r="AA30" t="s" s="2">
         <v>82</v>
       </c>
@@ -5370,7 +5366,7 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5385,31 +5381,31 @@
         <v>103</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AM30" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AM30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AN30" t="s" s="2">
+      <c r="AO30" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5428,16 +5424,16 @@
         <v>92</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5463,14 +5459,14 @@
         <v>82</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="Z31" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="Z31" t="s" s="2">
-        <v>314</v>
-      </c>
       <c r="AA31" t="s" s="2">
         <v>82</v>
       </c>
@@ -5487,7 +5483,7 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5496,7 +5492,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>103</v>
@@ -5505,24 +5501,24 @@
         <v>82</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5545,19 +5541,19 @@
         <v>92</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>320</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5606,7 +5602,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5624,10 +5620,10 @@
         <v>82</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>82</v>
@@ -5638,10 +5634,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5664,13 +5660,13 @@
         <v>92</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5721,7 +5717,7 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>91</v>
@@ -5736,31 +5732,31 @@
         <v>103</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>332</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5779,13 +5775,13 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5836,7 +5832,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5851,31 +5847,31 @@
         <v>103</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AL34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>341</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>342</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5894,13 +5890,13 @@
         <v>92</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5951,7 +5947,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5966,27 +5962,27 @@
         <v>103</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="AM35" t="s" s="2">
+      <c r="AN35" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AN35" t="s" s="2">
+      <c r="AO35" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>352</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6009,13 +6005,13 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>356</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6042,14 +6038,14 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Y36" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="Z36" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="Z36" t="s" s="2">
-        <v>358</v>
-      </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6066,7 +6062,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6087,25 +6083,25 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO36" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>360</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6124,13 +6120,13 @@
         <v>92</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6181,7 +6177,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6196,31 +6192,31 @@
         <v>103</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="AL37" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AM37" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>370</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6239,16 +6235,16 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>375</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>376</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6298,7 +6294,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6313,31 +6309,31 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>379</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>381</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6356,16 +6352,16 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6391,14 +6387,14 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6415,7 +6411,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6430,16 +6426,16 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>392</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6447,14 +6443,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6473,16 +6469,16 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6532,7 +6528,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6547,16 +6543,16 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>401</v>
-      </c>
       <c r="AN40" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -6564,10 +6560,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6590,13 +6586,13 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>403</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6623,14 +6619,14 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
       </c>
@@ -6647,7 +6643,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6668,10 +6664,10 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -6679,10 +6675,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6705,13 +6701,13 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6762,7 +6758,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6783,10 +6779,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -6794,10 +6790,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6820,16 +6816,16 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6855,14 +6851,14 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="Z43" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="Z43" t="s" s="2">
-        <v>418</v>
-      </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
       </c>
@@ -6879,7 +6875,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6894,16 +6890,16 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -6911,10 +6907,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6937,16 +6933,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6996,7 +6992,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7011,16 +7007,16 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AL44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>430</v>
-      </c>
       <c r="AN44" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7028,10 +7024,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7054,13 +7050,13 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7111,7 +7107,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7126,13 +7122,13 @@
         <v>103</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>82</v>
@@ -7143,14 +7139,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7169,16 +7165,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7228,7 +7224,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7243,13 +7239,13 @@
         <v>103</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AM46" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>82</v>
@@ -7260,10 +7256,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7286,16 +7282,16 @@
         <v>92</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7345,7 +7341,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7363,10 +7359,10 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>82</v>
@@ -7377,14 +7373,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7403,19 +7399,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7440,14 +7436,14 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Y48" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="Z48" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="Z48" t="s" s="2">
-        <v>461</v>
-      </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7464,7 +7460,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7482,24 +7478,24 @@
         <v>82</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO48" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>463</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7522,13 +7518,13 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7579,7 +7575,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7594,27 +7590,27 @@
         <v>103</v>
       </c>
       <c r="AK49" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AM49" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AM49" t="s" s="2">
+      <c r="AN49" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AO49" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>470</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7640,10 +7636,10 @@
         <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>472</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7694,7 +7690,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7712,10 +7708,10 @@
         <v>82</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>82</v>
@@ -7726,10 +7722,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7752,16 +7748,16 @@
         <v>82</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="L51" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="L51" t="s" s="2">
+      <c r="M51" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7811,7 +7807,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -7826,13 +7822,13 @@
         <v>103</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>187</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>82</v>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.3.0-dev</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-18</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -389,7 +389,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ServiceRequest.meta.versionId</t>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -1836,15 +1836,15 @@
   <dimension ref="A1:AO51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.71484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.71484375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="44.00390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.62109375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="30.62109375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="37.7265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1855,27 +1855,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="194.140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="67.80078125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="22.28515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.71484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="166.44140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="30.62109375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="85.41796875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="163.4453125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="66.88671875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="73.23046875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="140.125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="57.34375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -449,7 +449,7 @@
     <t>ServiceRequest.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -487,7 +487,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -545,7 +545,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -661,7 +661,7 @@
     <t>ServiceRequest.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -866,7 +866,7 @@
     <t>要求されたサービスの分類。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
     <t>RF1-5</t>
@@ -952,7 +952,7 @@
     <t>指定された個人、組織、または医療サービスによって実施できるテストやサービスのコード。ラボの場合、LOINCが（preferred）[http://build.fhir.org/terminologies.html#preferred]であり、LOINCオーダーコードを使用した値セットが[こちら]（valueset-diagnostic-requests.html）で利用可能です。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>Request.code</t>
@@ -989,7 +989,7 @@
     <t>注文コンテキストに基づくコード化された注文詳細。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -1129,7 +1129,7 @@
     <t>手続きを実行する前に満たされる必要がある前提条件を示すコード化された概念。たとえば、「痛み」、「フレアアップ時」など。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
@@ -1224,7 +1224,7 @@
     <t>初診医師」、「チームコーディネーター」、「介護者」など、ケアチーム内の個人の具体的責任を示します。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
   </si>
   <si>
     <t>Request.performerType</t>
@@ -1317,7 +1317,7 @@
     <t>サービス調査の依頼理由を正当化する診断または問題コード。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>Request.reasonCode</t>
@@ -1386,7 +1386,7 @@
 AOE</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1452,7 +1452,7 @@
     <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>targetSiteCode</t>
@@ -1498,7 +1498,7 @@
     <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
+++ b/jpcore-r4/develop/StructureDefinition-jp-servicerequest-common.xlsx
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -2699,7 +2699,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>126</v>
       </c>
@@ -7839,12 +7839,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO51">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
